--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.33813266172773</v>
+        <v>2.654946557530756</v>
       </c>
       <c r="D2" t="n">
-        <v>18.75526504222</v>
+        <v>3.047730569360751</v>
       </c>
       <c r="E2" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F2" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.00061461341419</v>
+        <v>4.062599874679806</v>
       </c>
       <c r="D3" t="n">
-        <v>22.68517697949688</v>
+        <v>3.686341259168244</v>
       </c>
       <c r="E3" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F3" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.06373808654647</v>
+        <v>5.860357439063802</v>
       </c>
       <c r="D4" t="n">
-        <v>35.79261252145631</v>
+        <v>5.81629953473665</v>
       </c>
       <c r="E4" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F4" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.16609194718914</v>
+        <v>3.926989941418236</v>
       </c>
       <c r="D5" t="n">
-        <v>19.15048286398049</v>
+        <v>3.11195346539683</v>
       </c>
       <c r="E5" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F5" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.30092538506503</v>
+        <v>6.386400375073067</v>
       </c>
       <c r="D6" t="n">
-        <v>33.5295462854535</v>
+        <v>5.448551271386194</v>
       </c>
       <c r="E6" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F6" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.13904400562972</v>
+        <v>4.08509465091483</v>
       </c>
       <c r="D7" t="n">
-        <v>38.56243815880519</v>
+        <v>6.266396200805843</v>
       </c>
       <c r="E7" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F7" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.10820992283197</v>
+        <v>6.517584112460196</v>
       </c>
       <c r="D8" t="n">
-        <v>49.89739468074625</v>
+        <v>8.108326635621266</v>
       </c>
       <c r="E8" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F8" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.09415550249955</v>
+        <v>1.640300269156177</v>
       </c>
       <c r="D9" t="n">
-        <v>10.81665382639197</v>
+        <v>1.757706246788695</v>
       </c>
       <c r="E9" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F9" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.2899783496721</v>
+        <v>4.272121481821716</v>
       </c>
       <c r="D10" t="n">
-        <v>4.392493429775566</v>
+        <v>0.7137801823385296</v>
       </c>
       <c r="E10" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F10" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34393286952185</v>
+        <v>2.655889091297301</v>
       </c>
       <c r="D11" t="n">
-        <v>41.35066856762491</v>
+        <v>6.719483642239049</v>
       </c>
       <c r="E11" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F11" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5.896281880463984</v>
+        <v>0.9581458055753975</v>
       </c>
       <c r="D12" t="n">
-        <v>5.159836669410733</v>
+        <v>0.8384734587792442</v>
       </c>
       <c r="E12" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F12" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.25397477562185</v>
+        <v>1.82877090103855</v>
       </c>
       <c r="D13" t="n">
-        <v>18.90625120968229</v>
+        <v>3.072265821573371</v>
       </c>
       <c r="E13" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F13" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.86640481084526</v>
+        <v>3.065790781762355</v>
       </c>
       <c r="D14" t="n">
-        <v>21.09502310972899</v>
+        <v>3.427941255330961</v>
       </c>
       <c r="E14" t="n">
-        <v>10.56610654710677</v>
+        <v>1.71699231390485</v>
       </c>
       <c r="F14" t="n">
-        <v>13.61269130004048</v>
+        <v>2.212062336256579</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
